--- a/data/merged/2026-09-28/MERGED_IT_Robot-Vacuum_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_IT_Robot-Vacuum_2026-09-28.xlsx
@@ -7771,50 +7771,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8140,7 +8096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -20526,251 +20482,6 @@
       <c r="BR50" s="13" t="inlineStr">
         <is>
           <t>小包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0C78DVSYP</t>
-        </is>
-      </c>
-      <c r="D51" s="14" t="inlineStr">
-        <is>
-          <t>Nome stile: Panni mocio</t>
-        </is>
-      </c>
-      <c r="E51" s="14" t="inlineStr">
-        <is>
-          <t>Colore: White | Marchio: dreame | Materiale: Tessuto | Tipo display: Analogico | Temperatura di funzionamento: 20 Gradi Celsius</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>dreame</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/DREAME/page/6460262E-9E3A-415B-B395-83EC96AB6666?lp_asin=B0C78DVSYP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>DREAME 4x Panni mocio di ricambio(×2 Paia) compatibili con X40Master/L10sUltraGen2/L50ProUltra/X50Master/L40sProUltra/L40UltraAE/D20Ultra/Matrix10Ultra/L10sUltraGen3/L10sProGen3 fino a 180 giri/min</t>
-        </is>
-      </c>
-      <c r="I51" s="14" t="inlineStr">
-        <is>
-          <t>Pulizia efficace dei pavimenti: I panni mop compatibili offrono una pulizia efficace dei pavimenti, consentendo di rimuovere lo sporco, le macchie e i residui da diverse superfici come legno, piastrelle e marmo; assicurano una pulizia profonda e una superficie brillante
-Materiale: I panni mop sono realizzati con materiali che assicurano una buona assorbenza dell'acqua e una durata nel tempo; sono resistenti e lavabili, consentendo di riutilizzarli più volte senza compromettere le prestazioni di pulizia
-Facili da installare e rimuovere: I panni mop sono progettati per essere facilmente installati e rimossi dai robot lavapavimenti L10sUltra/L10Ultra/L10Prime/L20Ultra/L10sProUltra/L10sProGen2/L10sPlus/X40Ultra/X30Ultra/X40Master/L10sUltraGen2/L40Ultra/L50ProUltra/X50Ultra/X50Master/L40sProUltra/L40UltraAE/D20Ultra/Matrix10Ultra/L10sUltraGen3/L10sProGen3, basta fissarli saldamente all'apposito supporto e iniziare la pulizia
-Adattabilità: I panni mop compatibili sono appositamente progettati per adattarsi in modo preciso e sicuro ai robot DREAME assicurando un'ottima aderenza al pavimento e una pulizia uniforme in tutte le direzioni
-Manutenzione semplice: Dopo l'uso, i panni mop possono essere facilmente rimossi e lavati per rimuovere lo sporco accumulato; questo assicura una manutenzione igienica e permette di riutilizzarli per molteplici sessioni di pulizia, offrendo risultati costanti nel tempo
-Compatibilità: L10sUltra/L10Ultra/L10Prime/L20Ultra/L10sProUltra/L10sProGen2/L10sPlus/X40Ultra/X30Ultra/X40Master/L10sUltraGen2/L40Ultra/L50ProUltra/X50Ultra/X50Master/L40sProUltra/L40UltraAE/D20Ultra/Matrix10Ultra/L10sUltraGen3/L10sProGen3</t>
-        </is>
-      </c>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0C78DVSYP?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71wCGkM+anL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0DJ1LN8L6</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere robot</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>7528</v>
-      </c>
-      <c r="P51" s="15">
-        <v>4139</v>
-      </c>
-      <c r="Q51" s="16">
-        <v>0.32</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Aspirapolvere robot</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="T51" s="15">
-        <v>127</v>
-      </c>
-      <c r="U51" s="16">
-        <v>-0.34</v>
-      </c>
-      <c r="V51" s="15">
-        <v>2348</v>
-      </c>
-      <c r="W51" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X51" s="15">
-        <v>990</v>
-      </c>
-      <c r="Y51" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>15.16</v>
-      </c>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="19">
-        <v>607</v>
-      </c>
-      <c r="AE51" s="15">
-        <v>8</v>
-      </c>
-      <c r="AF51" s="21">
-        <v>4.6</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0.063</v>
-      </c>
-      <c r="AH51" s="20">
-        <v>3.64</v>
-      </c>
-      <c r="AI51" s="16">
-        <v>0.65</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>1208</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN51" s="13" t="inlineStr">
-        <is>
-          <t>11天</t>
-        </is>
-      </c>
-      <c r="AO51" s="13"/>
-      <c r="AP51" s="4">
-        <v>12.11</v>
-      </c>
-      <c r="AQ51" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR51" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>40 g</t>
-        </is>
-      </c>
-      <c r="BK51" s="23" t="inlineStr">
-        <is>
-          <t>40.00 g</t>
-        </is>
-      </c>
-      <c r="BL51" s="23" t="inlineStr">
-        <is>
-          <t>15 x 15 x 15 cm</t>
-        </is>
-      </c>
-      <c r="BM51" s="23" t="inlineStr">
-        <is>
-          <t>15.00 x 15.00 x 15.00 cm</t>
-        </is>
-      </c>
-      <c r="BN51" s="23" t="inlineStr">
-        <is>
-          <t>70 g</t>
-        </is>
-      </c>
-      <c r="BO51" s="23" t="inlineStr">
-        <is>
-          <t>70.00 g</t>
-        </is>
-      </c>
-      <c r="BP51" s="23" t="inlineStr">
-        <is>
-          <t>14.5 x 14.4 x 4.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ51" s="23" t="inlineStr">
-        <is>
-          <t>14.50 x 14.40 x 4.20 cm</t>
-        </is>
-      </c>
-      <c r="BR51" s="13" t="inlineStr">
-        <is>
-          <t>超大号信封</t>
         </is>
       </c>
     </row>
@@ -21144,15 +20855,8 @@
     <hyperlink ref="M50" r:id="rId364" tooltip="https://www.amazon.it/b?node=733026031"/>
     <hyperlink ref="N50" r:id="rId365"/>
     <hyperlink ref="AW50" r:id="rId366" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2DL4PFUBEOZL"/>
-    <hyperlink ref="C51" r:id="rId367" tooltip="https://www.amazon.it/dp/B0C78DVSYP"/>
-    <hyperlink ref="G51" r:id="rId368" tooltip="https://www.amazon.it/stores/DREAME/page/6460262E-9E3A-415B-B395-83EC96AB6666?lp_asin=B0C78DVSYP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J51" r:id="rId369" tooltip="https://www.amazon.it/dp/B0C78DVSYP?psc=1"/>
-    <hyperlink ref="K51" r:id="rId370" tooltip="https://images-na.ssl-images-amazon.com/images/I/71wCGkM+anL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId371" tooltip="https://www.amazon.it/dp/B0DJ1LN8L6"/>
-    <hyperlink ref="M51" r:id="rId372" tooltip="https://www.amazon.it/b?node=733026031"/>
-    <hyperlink ref="N51" r:id="rId373"/>
   </hyperlinks>
-  <drawing r:id="rId374"/>
+  <drawing r:id="rId367"/>
 </worksheet>
 </file>
 
@@ -21211,18 +20915,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>11805</v>
+        <v>11678</v>
       </c>
       <c r="C2" s="15">
-        <v>5886218</v>
+        <v>5883870</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>498.62075391783145</v>
+        <v>503.8422675115602</v>
       </c>
       <c r="G2" s="22">
-        <v>0.3690561790727483</v>
+        <v>0.36654111738857503</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21243,7 +20947,7 @@
         <v>408.1890883241514</v>
       </c>
       <c r="G3" s="22">
-        <v>0.17591521555631975</v>
+        <v>0.17661644695543</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21264,7 +20968,7 @@
         <v>465.7599891274803</v>
       </c>
       <c r="G4" s="22">
-        <v>0.11501547503673368</v>
+        <v>0.11547394852479598</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21285,7 +20989,7 @@
         <v>304.89738955823293</v>
       </c>
       <c r="G5" s="22">
-        <v>0.15568824835089254</v>
+        <v>0.15630885122410546</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21306,7 +21010,7 @@
         <v>435.07855459544385</v>
       </c>
       <c r="G6" s="22">
-        <v>0.03979741770094101</v>
+        <v>0.039956057752667924</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21327,7 +21031,7 @@
         <v>265.0746753246753</v>
       </c>
       <c r="G7" s="22">
-        <v>0.03851564698158627</v>
+        <v>0.0386691776522285</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21348,7 +21052,7 @@
         <v>225.11704119850188</v>
       </c>
       <c r="G8" s="22">
-        <v>0.033388564104167316</v>
+        <v>0.03352165725047081</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21369,7 +21073,7 @@
         <v>145.5929978118162</v>
       </c>
       <c r="G9" s="22">
-        <v>0.014287054115734518</v>
+        <v>0.014344005021971125</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21390,7 +21094,7 @@
         <v>72.8994708994709</v>
       </c>
       <c r="G10" s="22">
-        <v>0.017725951167661864</v>
+        <v>0.017796610169491526</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21411,7 +21115,7 @@
         <v>139.98876404494382</v>
       </c>
       <c r="G11" s="22">
-        <v>0.008347141026041829</v>
+        <v>0.008380414312617702</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21432,7 +21136,7 @@
         <v>149.99086757990867</v>
       </c>
       <c r="G12" s="22">
-        <v>0.0068465314033826245</v>
+        <v>0.00687382297551789</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21453,7 +21157,7 @@
         <v>139.9904761904762</v>
       </c>
       <c r="G13" s="22">
-        <v>0.006565167099134023</v>
+        <v>0.006591337099811676</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21474,7 +21178,7 @@
         <v>184.09859154929578</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0044393034670334825</v>
+        <v>0.0044569993722536096</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21495,7 +21199,7 @@
         <v>139.99159663865547</v>
       </c>
       <c r="G15" s="22">
-        <v>0.0037202613561759467</v>
+        <v>0.0037350910232266167</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21516,7 +21220,7 @@
         <v>103.54729729729729</v>
       </c>
       <c r="G16" s="22">
-        <v>0.004626879669865883</v>
+        <v>0.004645323289391086</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21537,7 +21241,7 @@
         <v>129.99099099099098</v>
       </c>
       <c r="G17" s="22">
-        <v>0.0034701597523994123</v>
+        <v>0.0034839924670433146</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21558,7 +21262,7 @@
         <v>149.9879518072289</v>
       </c>
       <c r="G18" s="22">
-        <v>0.0025948041391815426</v>
+        <v>0.0026051475204017576</v>
       </c>
     </row>
   </sheetData>
@@ -21622,18 +21326,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>16636</v>
+        <v>16509</v>
       </c>
       <c r="C2" s="15">
-        <v>6391689</v>
+        <v>6389341</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>384.20828324116377</v>
+        <v>387.021685141438</v>
       </c>
       <c r="G2" s="22">
-        <v>0.5200862850533029</v>
+        <v>0.5181732580037665</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21654,7 +21358,7 @@
         <v>709.0</v>
       </c>
       <c r="G3" s="22">
-        <v>0.10663707131021978</v>
+        <v>0.10706214689265536</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21675,7 +21379,7 @@
         <v>404.76764036418814</v>
       </c>
       <c r="G4" s="22">
-        <v>0.16481695688873604</v>
+        <v>0.165473948524796</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21696,7 +21400,7 @@
         <v>304.89738955823293</v>
       </c>
       <c r="G5" s="22">
-        <v>0.15568824835089254</v>
+        <v>0.15630885122410546</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21717,7 +21421,7 @@
         <v>349.0</v>
       </c>
       <c r="G6" s="22">
-        <v>0.016819332853971927</v>
+        <v>0.016886377903327057</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21738,7 +21442,7 @@
         <v>290.02912621359224</v>
       </c>
       <c r="G7" s="22">
-        <v>0.009660174445868634</v>
+        <v>0.009698681732580037</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21759,7 +21463,7 @@
         <v>184.09859154929578</v>
       </c>
       <c r="G8" s="22">
-        <v>0.0044393034670334825</v>
+        <v>0.0044569993722536096</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21780,7 +21484,7 @@
         <v>139.99159663865547</v>
       </c>
       <c r="G9" s="22">
-        <v>0.0037202613561759467</v>
+        <v>0.0037350910232266167</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21801,7 +21505,7 @@
         <v>103.54729729729729</v>
       </c>
       <c r="G10" s="22">
-        <v>0.004626879669865883</v>
+        <v>0.004645323289391086</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21822,7 +21526,7 @@
         <v>129.99099099099098</v>
       </c>
       <c r="G11" s="22">
-        <v>0.0034701597523994123</v>
+        <v>0.0034839924670433146</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21843,7 +21547,7 @@
         <v>149.9879518072289</v>
       </c>
       <c r="G12" s="22">
-        <v>0.0025948041391815426</v>
+        <v>0.0026051475204017576</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21864,7 +21568,7 @@
         <v>15.0</v>
       </c>
       <c r="G13" s="22">
-        <v>0.007440522712351893</v>
+        <v>0.007470182046453233</v>
       </c>
     </row>
   </sheetData>
